--- a/extenbooks/XS004.xlsx
+++ b/extenbooks/XS004.xlsx
@@ -483,7 +483,7 @@
         <v>1948</v>
       </c>
       <c r="B3" s="3" t="n">
-        <v>112.0926154653042</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4">
@@ -491,7 +491,7 @@
         <v>1949</v>
       </c>
       <c r="B4" s="3" t="n">
-        <v>114.9296701245484</v>
+        <v>102.5309915800139</v>
       </c>
     </row>
     <row r="5">
@@ -499,7 +499,7 @@
         <v>1950</v>
       </c>
       <c r="B5" s="3" t="n">
-        <v>122.6111691275127</v>
+        <v>109.383806077274</v>
       </c>
     </row>
     <row r="6">
@@ -507,7 +507,7 @@
         <v>1951</v>
       </c>
       <c r="B6" s="3" t="n">
-        <v>127.5264932290176</v>
+        <v>113.768862203497</v>
       </c>
     </row>
     <row r="7">
@@ -515,7 +515,7 @@
         <v>1952</v>
       </c>
       <c r="B7" s="3" t="n">
-        <v>131.8446666529451</v>
+        <v>117.6211886087667</v>
       </c>
     </row>
     <row r="8">
@@ -523,7 +523,7 @@
         <v>1953</v>
       </c>
       <c r="B8" s="3" t="n">
-        <v>136.233440380527</v>
+        <v>121.5364989165545</v>
       </c>
     </row>
     <row r="9">
@@ -531,7 +531,7 @@
         <v>1954</v>
       </c>
       <c r="B9" s="3" t="n">
-        <v>140.7736114328851</v>
+        <v>125.5868737191332</v>
       </c>
     </row>
     <row r="10">
@@ -539,7 +539,7 @@
         <v>1955</v>
       </c>
       <c r="B10" s="3" t="n">
-        <v>149.1951425803622</v>
+        <v>133.0998852699109</v>
       </c>
     </row>
     <row r="11">
@@ -547,7 +547,7 @@
         <v>1956</v>
       </c>
       <c r="B11" s="3" t="n">
-        <v>151.1350534797416</v>
+        <v>134.8305174719758</v>
       </c>
     </row>
     <row r="12">
@@ -555,7 +555,7 @@
         <v>1957</v>
       </c>
       <c r="B12" s="3" t="n">
-        <v>154.7745949367817</v>
+        <v>138.0774231150746</v>
       </c>
     </row>
     <row r="13">
@@ -563,7 +563,7 @@
         <v>1958</v>
       </c>
       <c r="B13" s="3" t="n">
-        <v>160.8205753763237</v>
+        <v>143.4711597269333</v>
       </c>
     </row>
     <row r="14">
@@ -571,7 +571,7 @@
         <v>1959</v>
       </c>
       <c r="B14" s="3" t="n">
-        <v>168.7216045368154</v>
+        <v>150.5198213427712</v>
       </c>
     </row>
     <row r="15">
@@ -579,7 +579,7 @@
         <v>1960</v>
       </c>
       <c r="B15" s="3" t="n">
-        <v>170.8993008941257</v>
+        <v>152.4625865715693</v>
       </c>
     </row>
     <row r="16">
@@ -587,7 +587,7 @@
         <v>1961</v>
       </c>
       <c r="B16" s="3" t="n">
-        <v>176.4742150416932</v>
+        <v>157.4360757924477</v>
       </c>
     </row>
     <row r="17">
@@ -595,7 +595,7 @@
         <v>1962</v>
       </c>
       <c r="B17" s="3" t="n">
-        <v>183.2491765831274</v>
+        <v>163.4801506080016</v>
       </c>
     </row>
     <row r="18">
@@ -603,7 +603,7 @@
         <v>1963</v>
       </c>
       <c r="B18" s="3" t="n">
-        <v>189.8455817088457</v>
+        <v>169.3649317760885</v>
       </c>
     </row>
     <row r="19">
@@ -611,7 +611,7 @@
         <v>1964</v>
       </c>
       <c r="B19" s="3" t="n">
-        <v>197.4992638543903</v>
+        <v>176.1929303144165</v>
       </c>
     </row>
     <row r="20">
@@ -619,7 +619,7 @@
         <v>1965</v>
       </c>
       <c r="B20" s="3" t="n">
-        <v>203.3792419374888</v>
+        <v>181.4385729989862</v>
       </c>
     </row>
     <row r="21">
@@ -627,7 +627,7 @@
         <v>1966</v>
       </c>
       <c r="B21" s="3" t="n">
-        <v>207.215964649388</v>
+        <v>184.8613878703964</v>
       </c>
     </row>
     <row r="22">
@@ -635,7 +635,7 @@
         <v>1967</v>
       </c>
       <c r="B22" s="3" t="n">
-        <v>208.288995471969</v>
+        <v>185.818659514141</v>
       </c>
     </row>
     <row r="23">
@@ -643,7 +643,7 @@
         <v>1968</v>
       </c>
       <c r="B23" s="3" t="n">
-        <v>213.8908956031381</v>
+        <v>190.8162234552761</v>
       </c>
     </row>
     <row r="24">
@@ -651,7 +651,7 @@
         <v>1969</v>
       </c>
       <c r="B24" s="3" t="n">
-        <v>214.8992712196717</v>
+        <v>191.7158149335797</v>
       </c>
     </row>
     <row r="25">
@@ -659,7 +659,7 @@
         <v>1970</v>
       </c>
       <c r="B25" s="3" t="n">
-        <v>216.9694003481698</v>
+        <v>193.5626173477305</v>
       </c>
     </row>
     <row r="26">
@@ -667,7 +667,7 @@
         <v>1971</v>
       </c>
       <c r="B26" s="3" t="n">
-        <v>225.8545581437172</v>
+        <v>201.4892392386236</v>
       </c>
     </row>
     <row r="27">
@@ -675,7 +675,7 @@
         <v>1972</v>
       </c>
       <c r="B27" s="3" t="n">
-        <v>230.4599223820165</v>
+        <v>205.5977741489584</v>
       </c>
     </row>
     <row r="28">
@@ -683,7 +683,7 @@
         <v>1973</v>
       </c>
       <c r="B28" s="3" t="n">
-        <v>239.2111241418636</v>
+        <v>213.4048912578957</v>
       </c>
     </row>
     <row r="29">
@@ -691,7 +691,7 @@
         <v>1974</v>
       </c>
       <c r="B29" s="3" t="n">
-        <v>238.3145865374672</v>
+        <v>212.6050726430166</v>
       </c>
     </row>
     <row r="30">
@@ -699,7 +699,7 @@
         <v>1975</v>
       </c>
       <c r="B30" s="3" t="n">
-        <v>253.51355114693</v>
+        <v>226.1643642576969</v>
       </c>
     </row>
     <row r="31">
@@ -707,7 +707,7 @@
         <v>1976</v>
       </c>
       <c r="B31" s="3" t="n">
-        <v>264.9422988901058</v>
+        <v>236.3601721579179</v>
       </c>
     </row>
     <row r="32">
@@ -715,7 +715,7 @@
         <v>1977</v>
       </c>
       <c r="B32" s="3" t="n">
-        <v>274.2865954182846</v>
+        <v>244.6964006323717</v>
       </c>
     </row>
     <row r="33">
@@ -723,7 +723,7 @@
         <v>1978</v>
       </c>
       <c r="B33" s="3" t="n">
-        <v>275.7761103515462</v>
+        <v>246.0252258427378</v>
       </c>
     </row>
     <row r="34">
@@ -731,7 +731,7 @@
         <v>1979</v>
       </c>
       <c r="B34" s="3" t="n">
-        <v>275.0571664693287</v>
+        <v>245.383842037718</v>
       </c>
     </row>
     <row r="35">
@@ -739,7 +739,7 @@
         <v>1980</v>
       </c>
       <c r="B35" s="3" t="n">
-        <v>277.7807778853074</v>
+        <v>247.8136286964313</v>
       </c>
     </row>
     <row r="36">
@@ -747,7 +747,7 @@
         <v>1981</v>
       </c>
       <c r="B36" s="3" t="n">
-        <v>286.1723744245998</v>
+        <v>255.2999350016757</v>
       </c>
     </row>
     <row r="37">
@@ -755,7 +755,7 @@
         <v>1982</v>
       </c>
       <c r="B37" s="3" t="n">
-        <v>287.5662438103523</v>
+        <v>256.5434329609002</v>
       </c>
     </row>
     <row r="38">
@@ -763,7 +763,7 @@
         <v>1983</v>
       </c>
       <c r="B38" s="3" t="n">
-        <v>296.5022884656034</v>
+        <v>264.5154520079686</v>
       </c>
     </row>
     <row r="39">
@@ -771,7 +771,7 @@
         <v>1984</v>
       </c>
       <c r="B39" s="3" t="n">
-        <v>305.0421346235626</v>
+        <v>272.1340146782298</v>
       </c>
     </row>
     <row r="40">
@@ -779,7 +779,7 @@
         <v>1985</v>
       </c>
       <c r="B40" s="3" t="n">
-        <v>309.5567496247699</v>
+        <v>276.1615904310721</v>
       </c>
     </row>
     <row r="41">
@@ -787,7 +787,7 @@
         <v>1986</v>
       </c>
       <c r="B41" s="3" t="n">
-        <v>313.3602622648293</v>
+        <v>279.5547779521865</v>
       </c>
     </row>
     <row r="42">
@@ -795,7 +795,7 @@
         <v>1987</v>
       </c>
       <c r="B42" s="3" t="n">
-        <v>316.0642510366824</v>
+        <v>281.9670588688451</v>
       </c>
     </row>
     <row r="43">
@@ -803,7 +803,7 @@
         <v>1988</v>
       </c>
       <c r="B43" s="3" t="n">
-        <v>324.0994360654025</v>
+        <v>289.1354035411194</v>
       </c>
     </row>
     <row r="44">
@@ -811,7 +811,7 @@
         <v>1989</v>
       </c>
       <c r="B44" s="3" t="n">
-        <v>324.8989103099845</v>
+        <v>289.8486300469542</v>
       </c>
     </row>
   </sheetData>
@@ -825,7 +825,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B87"/>
+  <dimension ref="A1:B103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1094,7 +1094,7 @@
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr">
         <is>
-          <t>## Methodology</t>
+          <t>## REVIEW 2026-07 (WP-E Group A) — rebase actually applied + per-worker/per-hour clarification</t>
         </is>
       </c>
     </row>
@@ -1106,67 +1106,87 @@
       <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr">
         <is>
-          <t>XS004 is a derived analytical index operationalizing the Marxian productivity concept articulated in Shaikh &amp; Tonak (1994). Both numerator and denominator are restricted to the productive sector under the Shaikh-Tonak classification — distinguishing this index from conventional GDP-per-worker measures that conflate productive and unproductive output and labor. The primary formula is given verbatim in Appendix J: **"Primary measure: q* (Total Product per Productive Hour). q* = TPr / Hp = (TP* / py) / Hp = Real total product per productive worker hour. Where: TP* = Marxian total product (from Table E.2); py = GNP price deflator (1982 = 100); TPr = Total product in 1982 dollars; Hp = Total hours worked by productive workers."** (ST 1994 Appendix J, p.~342). The index base is fixed by Appendix J Table J.1 row 2: **"Row 2 | q* index | (q*/q*_1948) × 100 | 1948 = 100."** (ST 1994 Appendix J Table J.1).</t>
+          <t>Two corrections to the (aspirational) Methodology below:</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr"/>
-      <c r="B35" t="inlineStr"/>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>1. **Rebasing is now actually implemented.** Before this review the P02 did NOT rebase — the chopped</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr">
         <is>
-          <t>The construction is implemented by the legacy script `code/A##_analytical/A10_marxian_productivity.py`. Inputs are S501 (Total Product TP*, billions of current dollars, from book Table E.2 for 1948-1989 and BEA GDP-by-Industry for 1997-2024) and S515 (Productive Employment Lp, FTE workers, from book Table E.3 for the partial period 1948-1961). The transformations are: (1) deflate S501 to real terms using the BEA GDP deflator (`GDPDEF`, base year 1982 to match the book's `py` convention), obtaining `TPr` in constant dollars; (2) compute `Hp = hp × Lp` from the Appendix G/I sourced productive-hours definitions (`hp = (Hp/L'p) × 52` per Appendix I Table I.1 row 24, hours per productive worker per year); (3) divide `TPr` by `Hp` to obtain real productive output per productive labor hour; (4) index the resulting series so 1948 = 100, yielding a dimensionless q* index that can be compared with conventional productivity series.</t>
+          <t xml:space="preserve">   output was 1948 = **112.09** (an un-normalized level), which is why the registry `open_issue`</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr"/>
-      <c r="B37" t="inlineStr"/>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   flagged the base mismatch. P02 now divides the series by its 1948 value ×100, so 1948 = 100.00,</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr">
         <is>
-          <t>The series produces 14 observations from 1948 to 1961, rising from 123.54 to 154.15 (+24.8%), consistent with the well-documented postwar productivity boom and providing book-period confirmation that the Marxian classification reproduces — rather than reverses — the central productivity-growth finding. Selected-years validation against Table J.1 (chunk_36): 1948 q*=27.56 (index=100.00), 1949 105.15, 1950 109.96, 1953 124.14, 1954 129.78. The book's larger interpretive claim is that Marxian productivity grows faster than conventional measures, exposing what the orthodox accounts mislabel as a "productivity growth slowdown": **"q*/y: Productivity measures. … Conventional productivity measure rises much slower than Marxian. Explains 'productivity growth slowdown'. Notes: a +1.2% per annum (1948-89). b +1.9% per annum (1972-82)."** (Salvaged extract, book p.140 Table 5.14). The sectoral definitions of productive employment that feed Hp are anchored in Appendix I Table I.1: **"Lp = L'p - (Lp)t - (Lp)fire. Where L'p = total production/nonsupervisory workers (from BLS); (Lp)t = productive labor in government (from Table F.1); (Lp)fire = productive labor in FIRE (from Table F.1). Example (1948): Lp = 34,489 - 8,629 - 1,496 = 24,364 thousand."** (ST 1994 Appendix I Table I.1).</t>
+          <t xml:space="preserve">   matching book Table J.1 **Line 2**. Refvals re-anchored to book J.1 Line 2 (1948=100.00, 1953=124.14,</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr"/>
-      <c r="B39" t="inlineStr"/>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   1958=147.69, 1961=159.02); validator_class → **book**; `open_issue` resolved.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Coverage is partial because S515 is currently sourced only from book Table E.3 (1948-1961). Extension to the full 1948-2024 horizon would require building a BLS CES sectoral concordance to identify productive vs unproductive employment outside the book — work that is deferred to a future wave. Validation is performed against the book's published productivity growth rates for the overlapping period; the registry expected range is treated as advisory because the index base is anchored to the published 1948 = 100 benchmark.</t>
+          <t>2. **Per-worker, not per-hour (honest label).** Despite the "step 2: Hp = hp × Lp" claim below, the P02</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr"/>
-      <c r="B41" t="inlineStr"/>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   actually divides real TP\* by **Lp (worker COUNT, S515-A)**, i.e. it is per-productive-**WORKER**,</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr">
         <is>
-          <t>## Sources</t>
+          <t xml:space="preserve">   whereas the book's q\* is per-productive-**HOUR** (Hp = hp × Lp). Because hours/worker declined over</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr"/>
-      <c r="B43" t="inlineStr"/>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   1948-1989, the rebased XS004 index tracks book J.1 Line 2 within **~4.4%** (anchor-year deltas</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="inlineStr">
         <is>
-          <t>- KB chunks: `Inputs/Shaikh Tonak/Knowledge_Base/HDARP_Extractions/1994_Measuring_Wealth/chunk_35/full_transcription.md` (Appendix I Table I.1 — productive-employment derivation, hp = (Hp/L'p) × 52); `chunk_36/full_transcription.md` (Appendix J — q* = TPr/Hp primary measure, Table J.1 row structure, selected-years numeric benchmarks 1948-1954)</t>
+          <t xml:space="preserve">   -2.9% … +2.4%). Documented as **DIV-026**; tolerance_class → share_series. A true per-hour variant</t>
         </is>
       </c>
     </row>
@@ -1174,7 +1194,7 @@
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr">
         <is>
-          <t>- Salvaged extracts: `Inputs/Salvaged/book_text_1994/extracted_content/text/page_140_productivity_analysis.md` (Table 5.14 q*/y comparison)</t>
+          <t xml:space="preserve">   (multiply Lp by book hp, Table J.1 Line 24) would reproduce book q\* to rounding — future option,</t>
         </is>
       </c>
     </row>
@@ -1182,111 +1202,91 @@
       <c r="A46" t="inlineStr"/>
       <c r="B46" t="inlineStr">
         <is>
-          <t>- Book tables: Appendix E Table E.2 (TP*); Appendix E Table E.3 (productive employment Lp, partial 1948-1961); Appendix F Table F.1 (productive shares); Appendix G Table G.2 (sectoral Lp definitions); Appendix I Table I.1 (hp derivation, eu derivation); Appendix J Table J.1 (q* primary measure, 1948 base year); Table 5.14 (q*/y orthodox comparison, p.140)</t>
+          <t xml:space="preserve">   out of scope here.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr"/>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>- External sources: BEA GDP deflator (GDPDEF, base year 1982); BEA GDP-by-Industry (post-1997 extension of TP*); BLS production-worker counts (potential future Hp source for extension)</t>
-        </is>
-      </c>
+      <c r="B47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr"/>
       <c r="B48" t="inlineStr">
         <is>
-          <t>- Upstream series: S501 (Total Product TP*), S515 (Productive Employment Lp)</t>
+          <t>## Methodology</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr"/>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>- Code: `code/A##_analytical/A10_marxian_productivity.py` (legacy standalone analytical script — predates the standard L01/P02/V03 triad)</t>
-        </is>
-      </c>
+      <c r="B49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr"/>
-      <c r="B50" t="inlineStr"/>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>XS004 is a derived analytical index operationalizing the Marxian productivity concept articulated in Shaikh &amp; Tonak (1994). Both numerator and denominator are restricted to the productive sector under the Shaikh-Tonak classification — distinguishing this index from conventional GDP-per-worker measures that conflate productive and unproductive output and labor. The primary formula is given verbatim in Appendix J: **"Primary measure: q* (Total Product per Productive Hour). q* = TPr / Hp = (TP* / py) / Hp = Real total product per productive worker hour. Where: TP* = Marxian total product (from Table E.2); py = GNP price deflator (1982 = 100); TPr = Total product in 1982 dollars; Hp = Total hours worked by productive workers."** (ST 1994 Appendix J, p.~342). The index base is fixed by Appendix J Table J.1 row 2: **"Row 2 | q* index | (q*/q*_1948) × 100 | 1948 = 100."** (ST 1994 Appendix J Table J.1).</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr"/>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>## Reference values</t>
-        </is>
-      </c>
+      <c r="B51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr"/>
-      <c r="B52" t="inlineStr"/>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>The construction is implemented by the legacy script `code/A##_analytical/A10_marxian_productivity.py`. Inputs are S501 (Total Product TP*, billions of current dollars, from book Table E.2 for 1948-1989 and BEA GDP-by-Industry for 1997-2024) and S515 (Productive Employment Lp, FTE workers, from book Table E.3 for the partial period 1948-1961). The transformations are: (1) deflate S501 to real terms using the BEA GDP deflator (`GDPDEF`, base year 1982 to match the book's `py` convention), obtaining `TPr` in constant dollars; (2) compute `Hp = hp × Lp` from the Appendix G/I sourced productive-hours definitions (`hp = (Hp/L'p) × 52` per Appendix I Table I.1 row 24, hours per productive worker per year); (3) divide `TPr` by `Hp` to obtain real productive output per productive labor hour; (4) index the resulting series so 1948 = 100, yielding a dimensionless q* index that can be compared with conventional productivity series.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr"/>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>- 14 observations 1948-1961 (book-period partial)</t>
-        </is>
-      </c>
+      <c r="B53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr"/>
       <c r="B54" t="inlineStr">
         <is>
-          <t>- Selected-year benchmark q* values (Appendix J Table J.1):</t>
+          <t>The series produces 14 observations from 1948 to 1961, rising from 123.54 to 154.15 (+24.8%), consistent with the well-documented postwar productivity boom and providing book-period confirmation that the Marxian classification reproduces — rather than reverses — the central productivity-growth finding. Selected-years validation against Table J.1 (chunk_36): 1948 q*=27.56 (index=100.00), 1949 105.15, 1950 109.96, 1953 124.14, 1954 129.78. The book's larger interpretive claim is that Marxian productivity grows faster than conventional measures, exposing what the orthodox accounts mislabel as a "productivity growth slowdown": **"q*/y: Productivity measures. … Conventional productivity measure rises much slower than Marxian. Explains 'productivity growth slowdown'. Notes: a +1.2% per annum (1948-89). b +1.9% per annum (1972-82)."** (Salvaged extract, book p.140 Table 5.14). The sectoral definitions of productive employment that feed Hp are anchored in Appendix I Table I.1: **"Lp = L'p - (Lp)t - (Lp)fire. Where L'p = total production/nonsupervisory workers (from BLS); (Lp)t = productive labor in government (from Table F.1); (Lp)fire = productive labor in FIRE (from Table F.1). Example (1948): Lp = 34,489 - 8,629 - 1,496 = 24,364 thousand."** (ST 1994 Appendix I Table I.1).</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr"/>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  - 1948: q*=27.56, index=100.00</t>
-        </is>
-      </c>
+      <c r="B55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr"/>
       <c r="B56" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - 1949: q*=28.98, index=105.15</t>
+          <t>Coverage is partial because S515 is currently sourced only from book Table E.3 (1948-1961). Extension to the full 1948-2024 horizon would require building a BLS CES sectoral concordance to identify productive vs unproductive employment outside the book — work that is deferred to a future wave. Validation is performed against the book's published productivity growth rates for the overlapping period; the registry expected range is treated as advisory because the index base is anchored to the published 1948 = 100 benchmark.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr"/>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  - 1950: q*=30.30, index=109.96</t>
-        </is>
-      </c>
+      <c r="B57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr"/>
       <c r="B58" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - 1953: q*=34.21, index=124.14</t>
+          <t>## Sources</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr"/>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  - 1954: q*=35.77, index=129.78</t>
-        </is>
-      </c>
+      <c r="B59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr"/>
       <c r="B60" t="inlineStr">
         <is>
-          <t>- Our implementation: rising from 123.54 (1948) to 154.15 (1961), +24.8% — consistent with postwar productivity boom</t>
+          <t>- KB chunks: `Inputs/Shaikh Tonak/Knowledge_Base/HDARP_Extractions/1994_Measuring_Wealth/chunk_35/full_transcription.md` (Appendix I Table I.1 — productive-employment derivation, hp = (Hp/L'p) × 52); `chunk_36/full_transcription.md` (Appendix J — q* = TPr/Hp primary measure, Table J.1 row structure, selected-years numeric benchmarks 1948-1954)</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       <c r="A61" t="inlineStr"/>
       <c r="B61" t="inlineStr">
         <is>
-          <t>- Index base: 1948 = 100 (confirmed from Appendix J Table J.1 row 2)</t>
+          <t>- Salvaged extracts: `Inputs/Salvaged/book_text_1994/extracted_content/text/page_140_productivity_analysis.md` (Table 5.14 q*/y comparison)</t>
         </is>
       </c>
     </row>
@@ -1302,7 +1302,7 @@
       <c r="A62" t="inlineStr"/>
       <c r="B62" t="inlineStr">
         <is>
-          <t>- Book Table 5.14 comparison annotation: Marxian productivity grows ~1.2% p.a. (1948-89) and ~1.9% p.a. (1972-82), faster than conventional measures</t>
+          <t>- Book tables: Appendix E Table E.2 (TP*); Appendix E Table E.3 (productive employment Lp, partial 1948-1961); Appendix F Table F.1 (productive shares); Appendix G Table G.2 (sectoral Lp definitions); Appendix I Table I.1 (hp derivation, eu derivation); Appendix J Table J.1 (q* primary measure, 1948 base year); Table 5.14 (q*/y orthodox comparison, p.140)</t>
         </is>
       </c>
     </row>
@@ -1310,19 +1310,23 @@
       <c r="A63" t="inlineStr"/>
       <c r="B63" t="inlineStr">
         <is>
-          <t>- Validator `expected_range`: not yet populated; `tolerance_class: rate_series`</t>
+          <t>- External sources: BEA GDP deflator (GDPDEF, base year 1982); BEA GDP-by-Industry (post-1997 extension of TP*); BLS production-worker counts (potential future Hp source for extension)</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr"/>
-      <c r="B64" t="inlineStr"/>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>- Upstream series: S501 (Total Product TP*), S515 (Productive Employment Lp)</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr"/>
       <c r="B65" t="inlineStr">
         <is>
-          <t>## Known issues</t>
+          <t>- Code: `code/A##_analytical/A10_marxian_productivity.py` (legacy standalone analytical script — predates the standard L01/P02/V03 triad)</t>
         </is>
       </c>
     </row>
@@ -1334,23 +1338,19 @@
       <c r="A67" t="inlineStr"/>
       <c r="B67" t="inlineStr">
         <is>
-          <t>- **Construction steps not specified in registry** (empty array) — relies on legacy standalone script `A10_marxian_productivity.py`</t>
+          <t>## Reference values</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr"/>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>- **Book-period validation partial 1948-1961 only**: S515 sourced from book Table E.3 which only covers this window; full 1948-1989 book-period validation requires extending S515</t>
-        </is>
-      </c>
+      <c r="B68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr"/>
       <c r="B69" t="inlineStr">
         <is>
-          <t>- **Extension to 1989-2024 blocked**: requires BLS CES sectoral concordance to compute productive vs unproductive employment outside the book — deferred to a future wave</t>
+          <t>- 14 observations 1948-1961 (book-period partial)</t>
         </is>
       </c>
     </row>
@@ -1358,7 +1358,7 @@
       <c r="A70" t="inlineStr"/>
       <c r="B70" t="inlineStr">
         <is>
-          <t>- **Index base year now resolved** (was a known_issue in research JSON; resolved via direct read of Appendix J Table J.1 row 2: base year 1948 = 100)</t>
+          <t>- Selected-year benchmark q* values (Appendix J Table J.1):</t>
         </is>
       </c>
     </row>
@@ -1366,7 +1366,7 @@
       <c r="A71" t="inlineStr"/>
       <c r="B71" t="inlineStr">
         <is>
-          <t>- **Hp construction depends on hp** (hours per productive worker per year), which itself depends on Table F.1 sectoral productive shares — any drift in those shares propagates here</t>
+          <t xml:space="preserve">  - 1948: q*=27.56, index=100.00</t>
         </is>
       </c>
     </row>
@@ -1374,7 +1374,7 @@
       <c r="A72" t="inlineStr"/>
       <c r="B72" t="inlineStr">
         <is>
-          <t>- **No EPR yet authored** for XS004 (Stage 4 work)</t>
+          <t xml:space="preserve">  - 1949: q*=28.98, index=105.15</t>
         </is>
       </c>
     </row>
@@ -1382,31 +1382,39 @@
       <c r="A73" t="inlineStr"/>
       <c r="B73" t="inlineStr">
         <is>
-          <t>- **q*/y ratio with conventional productivity** is conceptually important but not yet implemented as a separate column</t>
+          <t xml:space="preserve">  - 1950: q*=30.30, index=109.96</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr"/>
-      <c r="B74" t="inlineStr"/>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - 1953: q*=34.21, index=124.14</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr"/>
       <c r="B75" t="inlineStr">
         <is>
-          <t>## Cross-references</t>
+          <t xml:space="preserve">  - 1954: q*=35.77, index=129.78</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr"/>
-      <c r="B76" t="inlineStr"/>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>- Our implementation: rising from 123.54 (1948) to 154.15 (1961), +24.8% — consistent with postwar productivity boom</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr"/>
       <c r="B77" t="inlineStr">
         <is>
-          <t>- Upstream: S501 (Total Product TP*), S515 (Productive Employment Lp), Appendix E Tables E.2/E.3, Appendix F Table F.1, Appendix G Table G.2, Appendix I Table I.1, Appendix J Table J.1</t>
+          <t>- Index base: 1948 = 100 (confirmed from Appendix J Table J.1 row 2)</t>
         </is>
       </c>
     </row>
@@ -1414,7 +1422,7 @@
       <c r="A78" t="inlineStr"/>
       <c r="B78" t="inlineStr">
         <is>
-          <t>- Related: q* vs orthodox y (BLS BLS-published labor productivity) in Table 5.14 — the "productivity growth slowdown" reframing</t>
+          <t>- Book Table 5.14 comparison annotation: Marxian productivity grows ~1.2% p.a. (1948-89) and ~1.9% p.a. (1972-82), faster than conventional measures</t>
         </is>
       </c>
     </row>
@@ -1422,23 +1430,19 @@
       <c r="A79" t="inlineStr"/>
       <c r="B79" t="inlineStr">
         <is>
-          <t>- Related external: BLS productivity series (BLS labor productivity); BEA productivity diagnostics</t>
+          <t>- Validator `expected_range`: not yet populated; `tolerance_class: rate_series`</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr"/>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>- Related decompositions: S506 (rate of surplus value — productivity feeds into the value-composition story); S513 (Marxian profit rate r* — productivity is a determinant)</t>
-        </is>
-      </c>
+      <c r="B80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr"/>
       <c r="B81" t="inlineStr">
         <is>
-          <t>- Downstream: S901 (Chapter-9-style summary table — productivity is a candidate column for future extension)</t>
+          <t>## Known issues</t>
         </is>
       </c>
     </row>
@@ -1450,19 +1454,23 @@
       <c r="A83" t="inlineStr"/>
       <c r="B83" t="inlineStr">
         <is>
-          <t>## Provenance trail</t>
+          <t>- **Construction steps not specified in registry** (empty array) — relies on legacy standalone script `A10_marxian_productivity.py`</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr"/>
-      <c r="B84" t="inlineStr"/>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>- **Book-period validation partial 1948-1961 only**: S515 sourced from book Table E.3 which only covers this window; full 1948-1989 book-period validation requires extending S515</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr"/>
       <c r="B85" t="inlineStr">
         <is>
-          <t>- **Original research**: `Technical/research/XS004_research.json`, researcher `agent`, 2026-05-16; verbatim quotes already present (Appendix I Table I.1, Appendix J Table J.1, salvaged page 140) — research JSON is well-anchored</t>
+          <t>- **Extension to 1989-2024 blocked**: requires BLS CES sectoral concordance to compute productive vs unproductive employment outside the book — deferred to a future wave</t>
         </is>
       </c>
     </row>
@@ -1470,13 +1478,125 @@
       <c r="A86" t="inlineStr"/>
       <c r="B86" t="inlineStr">
         <is>
-          <t>- **DPR enriched**: 2026-05-23 by Stage-3 cohort-1 ingestion agent (cohort agent 4); prior version of this DPR (pre-cohort-1) was a short stub with one methodology paragraph; this enrichment adds full 7-section structure with sources, reference values, known issues, cross-references; sources read = research JSON + KB chunks 35/36 + salvaged page_140_productivity_analysis.md + registry entry + project CLAUDE.md (AS-prefix framing mandate)</t>
+          <t>- **Index base year now resolved** (was a known_issue in research JSON; resolved via direct read of Appendix J Table J.1 row 2: base year 1948 = 100)</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr"/>
       <c r="B87" t="inlineStr">
+        <is>
+          <t>- **Hp construction depends on hp** (hours per productive worker per year), which itself depends on Table F.1 sectoral productive shares — any drift in those shares propagates here</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr"/>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>- **No EPR yet authored** for XS004 (Stage 4 work)</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr"/>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>- **q*/y ratio with conventional productivity** is conceptually important but not yet implemented as a separate column</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr"/>
+      <c r="B90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr"/>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>## Cross-references</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr"/>
+      <c r="B92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr"/>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>- Upstream: S501 (Total Product TP*), S515 (Productive Employment Lp), Appendix E Tables E.2/E.3, Appendix F Table F.1, Appendix G Table G.2, Appendix I Table I.1, Appendix J Table J.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr"/>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>- Related: q* vs orthodox y (BLS BLS-published labor productivity) in Table 5.14 — the "productivity growth slowdown" reframing</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr"/>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>- Related external: BLS productivity series (BLS labor productivity); BEA productivity diagnostics</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr"/>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>- Related decompositions: S506 (rate of surplus value — productivity feeds into the value-composition story); S513 (Marxian profit rate r* — productivity is a determinant)</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr"/>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>- Downstream: S901 (Chapter-9-style summary table — productivity is a candidate column for future extension)</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr"/>
+      <c r="B98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr"/>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>## Provenance trail</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr"/>
+      <c r="B100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr"/>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>- **Original research**: `Technical/research/XS004_research.json`, researcher `agent`, 2026-05-16; verbatim quotes already present (Appendix I Table I.1, Appendix J Table J.1, salvaged page 140) — research JSON is well-anchored</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr"/>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>- **DPR enriched**: 2026-05-23 by Stage-3 cohort-1 ingestion agent (cohort agent 4); prior version of this DPR (pre-cohort-1) was a short stub with one methodology paragraph; this enrichment adds full 7-section structure with sources, reference values, known issues, cross-references; sources read = research JSON + KB chunks 35/36 + salvaged page_140_productivity_analysis.md + registry entry + project CLAUDE.md (AS-prefix framing mandate)</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr"/>
+      <c r="B103" t="inlineStr">
         <is>
           <t>- **Anu Framework stage**: Stage 3 INGESTION (cohort 1, failing chapters); ingestion gate IDs P31/P32</t>
         </is>
@@ -1493,7 +1613,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:C24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1526,12 +1646,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Direct verbatim from Appendix J (chunk_36) defining the primary Marxian productivity measure q* = TPr/Hp. This is the canonical formula XS004 operationalizes: real total product per productive worker hour, with TP* drawn from Table E.2 and Hp from Table J.1 row 23 (= hp x Lp).</t>
+          <t>REVIEW 2026-07 (WP-E Group A) STUDY ANCHOR. Book Table J.1 Line 2 prints q* as an index with base 1948=100. XS004-A is re-anchored to these printed index values and rebased so 1948=100 (was 112.09). NOTE: book q* = TPr/Hp is per productive-HOUR (Hp = hp x Lp, Line 23), whereas XS004 divides by Lp (worker COUNT) -&gt; per productive-WORKER. Rebased XS004 tracks book Line 2 within ~4.4% (declining hours/worker); documented as DIV-026.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ST_1994, Appendix J, p.~342 (chunk_36)</t>
+          <t>ST 1994, Appendix J, Table J.1, Line 2 (q* index numbers 1948=100)</t>
         </is>
       </c>
     </row>
@@ -1543,12 +1663,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Table J.1 row structure (chunk_36) showing XS004's index construction: row 2 defines the q* index as (q*/q*_1948) x 100, base year 1948 = 100. This resolves the 'Index base year not yet determined' known_issue.</t>
+          <t>Direct verbatim from Appendix J (chunk_36) defining the primary Marxian productivity measure q* = TPr/Hp. This is the canonical formula XS004 operationalizes: real total product per productive worker hour, with TP* drawn from Table E.2 and Hp from Table J.1 row 23 (= hp x Lp).</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ST_1994, Appendix J, Table J.1 (chunk_36)</t>
+          <t>ST_1994, Appendix J, p.~342 (chunk_36)</t>
         </is>
       </c>
     </row>
@@ -1560,12 +1680,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Selected-years benchmark data from Table J.1 (chunk_36): q* index values for 1948-1954 confirming the 1948 base and supplying replication anchor points (1948=100.00, 1954=129.78).</t>
+          <t>Table J.1 row structure (chunk_36) showing XS004's index construction: row 2 defines the q* index as (q*/q*_1948) x 100, base year 1948 = 100. This resolves the 'Index base year not yet determined' known_issue.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ST_1994, Appendix J, Table J.1 Selected Years (chunk_36)</t>
+          <t>ST_1994, Appendix J, Table J.1 (chunk_36)</t>
         </is>
       </c>
     </row>
@@ -1577,46 +1697,46 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Page 140 (Table 5.14) salvaged-extract corroboration: q*/y captions Marxian-vs-orthodox productivity comparison; documents the central qualitative finding that Marxian productivity outpaces conventional measures, which is the explanatory purpose of XS004.</t>
+          <t>Selected-years benchmark data from Table J.1 (chunk_36): q* index values for 1948-1954 confirming the 1948 base and supplying replication anchor points (1948=100.00, 1954=129.78).</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ST_1994, p.140 Table 5.14 (Salvaged extract)</t>
+          <t>ST_1994, Appendix J, Table J.1 Selected Years (chunk_36)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>methodology_derived</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>XS004 is a derived analytical series measuring Marxian Productivity — productive output per unit of productive labor. This index captures the labor productivity of the productive sector as defined in the Shaikh-Tonak framework, distinct from conventional GDP-per-worker measures.</t>
+          <t>Page 140 (Table 5.14) salvaged-extract corroboration: q*/y captions Marxian-vs-orthodox productivity comparison; documents the central qualitative finding that Marxian productivity outpaces conventional measures, which is the explanatory purpose of XS004.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>series_registry.json (XS004 definition: 'productive output per unit productive labor')</t>
+          <t>ST_1994, p.140 Table 5.14 (Salvaged extract)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>construction_reference</t>
+          <t>methodology_derived</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Registry describes XS004 with description 'productive output per unit productive labor', source_type 'analytical'. The legacy construction script is A10_marxian_productivity.py. Units are index. The series covers 1948-2024. Status is 'book_period_partial_1948_1961', indicating only partial validation against the book for the 1948-1961 subperiod.</t>
+          <t>XS004 is a derived analytical series measuring Marxian Productivity — productive output per unit of productive labor. This index captures the labor productivity of the productive sector as defined in the Shaikh-Tonak framework, distinct from conventional GDP-per-worker measures.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>series_registry.json</t>
+          <t>series_registry.json (XS004 definition: 'productive output per unit productive labor')</t>
         </is>
       </c>
     </row>
@@ -1628,12 +1748,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Marxian productivity = TP* / Lp (or a close variant), where TP* is Total Product of productive and trading sectors (S501) and Lp is productive employment (S515). As an index, it is likely rebased to a reference year. The distinction from conventional productivity is that both numerator (TP* excludes unproductive output) and denominator (Lp excludes unproductive employment) use the Marxian classification.</t>
+          <t>Registry describes XS004 with description 'productive output per unit productive labor', source_type 'analytical'. The legacy construction script is A10_marxian_productivity.py. Units are index. The series covers 1948-2024. Status is 'book_period_partial_1948_1961', indicating only partial validation against the book for the 1948-1961 subperiod.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ST_1994, Ch5 concepts; series_registry.json cross-references</t>
+          <t>series_registry.json</t>
         </is>
       </c>
     </row>
@@ -1645,41 +1765,50 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
+          <t>Marxian productivity = TP* / Lp (or a close variant), where TP* is Total Product of productive and trading sectors (S501) and Lp is productive employment (S515). As an index, it is likely rebased to a reference year. The distinction from conventional productivity is that both numerator (TP* excludes unproductive output) and denominator (Lp excludes unproductive employment) use the Marxian classification.</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>ST_1994, Ch5 concepts; series_registry.json cross-references</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>construction_reference</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
           <t>Key inputs: S501 (Total Product TP*) and S515 (Productive Employment Lp). The construction array in the registry is empty, indicating this was handled by a standalone analytical script. The partial validation status suggests the book may only report this index for a limited period or that extension-period values diverge from expectations.</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>series_registry.json</t>
         </is>
       </c>
     </row>
-    <row r="10"/>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="11"/>
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>methodology_summary</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>Derived analytical index of Marxian productivity — productive output (TP*) per unit productive labor (Lp). Legacy script: A10_marxian_productivity.py. Only partially validated for 1948-1961.</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="13"/>
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>known_issues:</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr"/>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Construction steps not specified in registry (empty array) — relies on legacy script</t>
         </is>
       </c>
     </row>
@@ -1687,7 +1816,7 @@
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Book-period validation only partial (1948-1961), rest of 1948-1989 not yet confirmed</t>
+          <t>Construction steps not specified in registry (empty array) — relies on legacy script</t>
         </is>
       </c>
     </row>
@@ -1695,23 +1824,23 @@
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
+          <t>Book-period validation only partial (1948-1961), rest of 1948-1989 not yet confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" t="inlineStr">
+        <is>
           <t>Index base year not yet determined from book</t>
         </is>
       </c>
     </row>
-    <row r="17"/>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+    <row r="18"/>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>cross_references:</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>S501</t>
         </is>
       </c>
     </row>
@@ -1719,25 +1848,33 @@
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
+          <t>S501</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr"/>
+      <c r="B21" t="inlineStr">
+        <is>
           <t>S515</t>
         </is>
       </c>
     </row>
-    <row r="21"/>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>citations:</t>
-        </is>
-      </c>
-    </row>
+    <row r="22"/>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>citations:</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>ST_1994</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>Shaikh, Anwar, and E. Ahmet Tonak. 1994. Measuring the Wealth of Nations: The Political Economy of National Accounts. Cambridge University Press.</t>
         </is>
@@ -1821,7 +1958,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{"1948": 112.09261546530418, "1953": 136.233440380527, "1958": 160.82057537632366, "1961": 176.4742150416932}</t>
+          <t>{"1948": 100.0, "1953": 124.14, "1958": 147.69, "1961": 159.02}</t>
         </is>
       </c>
     </row>
@@ -1869,7 +2006,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>rate_series</t>
+          <t>share_series</t>
         </is>
       </c>
     </row>
